--- a/public/import_vien_com.xlsx
+++ b/public/import_vien_com.xlsx
@@ -30,11 +30,9 @@
       <text>
         <r>
           <rPr>
-            <sz val="9"/>
-            <color rgb="FF000000"/>
-            <rFont val="Tahoma"/>
+            <sz val="10"/>
+            <rFont val="Arial"/>
             <family val="2"/>
-            <charset val="1"/>
           </rPr>
           <t xml:space="preserve">cốm màu gì? Hoạt chât gì? (nếu viên 2 màu, nhiều hoạt chất)</t>
         </r>
@@ -65,12 +63,9 @@
       <text>
         <r>
           <rPr>
-            <b val="true"/>
-            <sz val="9"/>
-            <color rgb="FF000000"/>
-            <rFont val="Tahoma"/>
+            <sz val="10"/>
+            <rFont val="Arial"/>
             <family val="2"/>
-            <charset val="1"/>
           </rPr>
           <t xml:space="preserve">Admin:
 </t>
@@ -113,11 +108,9 @@
       <text>
         <r>
           <rPr>
-            <sz val="9"/>
-            <color rgb="FF000000"/>
-            <rFont val="Tahoma"/>
+            <sz val="10"/>
+            <rFont val="Arial"/>
             <family val="2"/>
-            <charset val="1"/>
           </rPr>
           <t xml:space="preserve">đóng chai, ép vỉ, ép gói</t>
         </r>
@@ -148,12 +141,9 @@
       <text>
         <r>
           <rPr>
-            <b val="true"/>
-            <sz val="9"/>
-            <color rgb="FF000000"/>
-            <rFont val="Tahoma"/>
+            <sz val="10"/>
+            <rFont val="Arial"/>
             <family val="2"/>
-            <charset val="1"/>
           </rPr>
           <t xml:space="preserve">Admin:
 </t>
@@ -196,12 +186,9 @@
       <text>
         <r>
           <rPr>
-            <b val="true"/>
-            <sz val="9"/>
-            <color rgb="FF000000"/>
-            <rFont val="Tahoma"/>
+            <sz val="10"/>
+            <rFont val="Arial"/>
             <family val="2"/>
-            <charset val="1"/>
           </rPr>
           <t xml:space="preserve">Admin:
 </t>
@@ -243,12 +230,9 @@
       <text>
         <r>
           <rPr>
-            <b val="true"/>
-            <sz val="9"/>
-            <color rgb="FF000000"/>
-            <rFont val="Tahoma"/>
+            <sz val="10"/>
+            <rFont val="Arial"/>
             <family val="2"/>
-            <charset val="1"/>
           </rPr>
           <t xml:space="preserve">Admin:
 </t>
@@ -291,12 +275,9 @@
       <text>
         <r>
           <rPr>
-            <b val="true"/>
-            <sz val="9"/>
-            <color rgb="FF000000"/>
-            <rFont val="Tahoma"/>
+            <sz val="10"/>
+            <rFont val="Arial"/>
             <family val="2"/>
-            <charset val="1"/>
           </rPr>
           <t xml:space="preserve">Admin:
 </t>
@@ -338,12 +319,9 @@
       <text>
         <r>
           <rPr>
-            <b val="true"/>
-            <sz val="9"/>
-            <color rgb="FF000000"/>
-            <rFont val="Tahoma"/>
+            <sz val="10"/>
+            <rFont val="Arial"/>
             <family val="2"/>
-            <charset val="1"/>
           </rPr>
           <t xml:space="preserve">Admin:
 </t>
@@ -385,12 +363,9 @@
       <text>
         <r>
           <rPr>
-            <b val="true"/>
-            <sz val="9"/>
-            <color rgb="FF000000"/>
-            <rFont val="Tahoma"/>
+            <sz val="10"/>
+            <rFont val="Arial"/>
             <family val="2"/>
-            <charset val="1"/>
           </rPr>
           <t xml:space="preserve">Admin:
 </t>
@@ -434,7 +409,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="177" uniqueCount="150">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="179" uniqueCount="150">
   <si>
     <t xml:space="preserve">STT</t>
   </si>
@@ -907,11 +882,12 @@
     <numFmt numFmtId="173" formatCode="0.0%"/>
     <numFmt numFmtId="174" formatCode="0.000%"/>
   </numFmts>
-  <fonts count="14">
+  <fonts count="13">
     <font>
       <sz val="10"/>
       <name val="Arial"/>
       <family val="2"/>
+      <charset val="1"/>
     </font>
     <font>
       <sz val="10"/>
@@ -927,12 +903,6 @@
       <sz val="10"/>
       <name val="Arial"/>
       <family val="0"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <name val="Arial"/>
-      <family val="2"/>
-      <charset val="1"/>
     </font>
     <font>
       <b val="true"/>
@@ -984,14 +954,11 @@
       <charset val="1"/>
     </font>
     <font>
-      <sz val="9"/>
-      <color rgb="FF000000"/>
-      <name val="Tahoma"/>
+      <sz val="10"/>
+      <name val="Arial"/>
       <family val="2"/>
-      <charset val="1"/>
     </font>
     <font>
-      <b val="true"/>
       <sz val="9"/>
       <color rgb="FF000000"/>
       <name val="Tahoma"/>
@@ -1104,269 +1071,277 @@
     <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="65">
+  <cellXfs count="67">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="true"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="5" fillId="2" borderId="1" xfId="20" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="165" fontId="4" fillId="2" borderId="1" xfId="20" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="5" fillId="3" borderId="1" xfId="20" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="165" fontId="4" fillId="3" borderId="1" xfId="20" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="4" borderId="1" xfId="20" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="4" fillId="4" borderId="1" xfId="20" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="5" borderId="1" xfId="20" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="4" fillId="5" borderId="1" xfId="20" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="166" fontId="5" fillId="3" borderId="1" xfId="20" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="166" fontId="4" fillId="3" borderId="1" xfId="20" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="5" fillId="6" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="165" fontId="4" fillId="6" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="7" fillId="6" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="165" fontId="6" fillId="6" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="7" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="165" fontId="6" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="true"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="7" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="165" fontId="6" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="7" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="165" fontId="6" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="true"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="7" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="165" fontId="6" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="167" fontId="7" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="167" fontId="6" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="7" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="165" fontId="6" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="8" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="165" fontId="7" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="166" fontId="7" fillId="6" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="166" fontId="6" fillId="6" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="166" fontId="7" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="166" fontId="6" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="168" fontId="7" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="168" fontId="6" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="4" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="4" fillId="4" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="166" fontId="5" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="166" fontId="4" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="166" fontId="5" fillId="4" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="166" fontId="4" fillId="4" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="5" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="4" fillId="5" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="166" fontId="5" fillId="5" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="166" fontId="4" fillId="5" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="5" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="165" fontId="4" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="9" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="165" fontId="8" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="169" fontId="5" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="169" fontId="4" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="166" fontId="5" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="166" fontId="4" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="168" fontId="5" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="168" fontId="4" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="170" fontId="5" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="170" fontId="4" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="166" fontId="5" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="166" fontId="4" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="4" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="166" fontId="5" fillId="3" borderId="4" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="166" fontId="4" fillId="3" borderId="4" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="true"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="165" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="171" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="171" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="9" fillId="7" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="165" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="true"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="167" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="167" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="167" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="165" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="true"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="165" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="10" fillId="7" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="166" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="true"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="166" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="165" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="168" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="172" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="166" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="168" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="170" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="166" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="166" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="171" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="true"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="167" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="167" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="165" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="true"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="165" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="167" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="165" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="true"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="165" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="165" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="165" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="165" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="true"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="173" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="166" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="true"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="166" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="174" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="168" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="172" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="166" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="168" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="170" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="166" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="166" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="171" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="165" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="165" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="165" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="165" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="true"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="173" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="174" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="174" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="174" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -2011,7 +1986,9 @@
       <c r="C4" s="37" t="s">
         <v>77</v>
       </c>
-      <c r="D4" s="38"/>
+      <c r="D4" s="38" t="n">
+        <v>1</v>
+      </c>
       <c r="E4" s="39" t="s">
         <v>78</v>
       </c>
@@ -2142,7 +2119,9 @@
       <c r="C5" s="57" t="s">
         <v>87</v>
       </c>
-      <c r="D5" s="44"/>
+      <c r="D5" s="58" t="s">
+        <v>76</v>
+      </c>
       <c r="E5" s="39" t="s">
         <v>78</v>
       </c>
@@ -2171,7 +2150,7 @@
       <c r="P5" s="51" t="n">
         <v>0.029</v>
       </c>
-      <c r="Q5" s="38"/>
+      <c r="Q5" s="59"/>
       <c r="R5" s="47"/>
       <c r="S5" s="48" t="s">
         <v>89</v>
@@ -2270,11 +2249,11 @@
         <v>3</v>
       </c>
       <c r="B6" s="36"/>
-      <c r="C6" s="58" t="s">
+      <c r="C6" s="60" t="s">
         <v>93</v>
       </c>
-      <c r="D6" s="44"/>
-      <c r="E6" s="59" t="s">
+      <c r="D6" s="58"/>
+      <c r="E6" s="61" t="s">
         <v>94</v>
       </c>
       <c r="F6" s="40" t="s">
@@ -2429,14 +2408,16 @@
         <v>4</v>
       </c>
       <c r="B7" s="36"/>
-      <c r="C7" s="58" t="s">
+      <c r="C7" s="60" t="s">
         <v>119</v>
       </c>
-      <c r="D7" s="44"/>
-      <c r="E7" s="60" t="s">
+      <c r="D7" s="58" t="s">
+        <v>76</v>
+      </c>
+      <c r="E7" s="62" t="s">
         <v>120</v>
       </c>
-      <c r="F7" s="61" t="s">
+      <c r="F7" s="63" t="s">
         <v>121</v>
       </c>
       <c r="G7" s="41" t="s">
@@ -2514,7 +2495,7 @@
       <c r="AU7" s="53" t="n">
         <v>6</v>
       </c>
-      <c r="AV7" s="62" t="n">
+      <c r="AV7" s="64" t="n">
         <v>0.962</v>
       </c>
       <c r="AW7" s="52" t="n">
@@ -2526,7 +2507,7 @@
       <c r="AY7" s="52" t="n">
         <v>101.8</v>
       </c>
-      <c r="AZ7" s="62" t="n">
+      <c r="AZ7" s="64" t="n">
         <v>1.019</v>
       </c>
       <c r="BA7" s="54" t="n">
@@ -2576,14 +2557,14 @@
         <v>5</v>
       </c>
       <c r="B8" s="36"/>
-      <c r="C8" s="58" t="s">
+      <c r="C8" s="60" t="s">
         <v>130</v>
       </c>
-      <c r="D8" s="44"/>
-      <c r="E8" s="60" t="s">
+      <c r="D8" s="58"/>
+      <c r="E8" s="62" t="s">
         <v>131</v>
       </c>
-      <c r="F8" s="60" t="s">
+      <c r="F8" s="62" t="s">
         <v>132</v>
       </c>
       <c r="G8" s="41" t="s">
@@ -2675,32 +2656,32 @@
       <c r="AU8" s="53" t="n">
         <v>8</v>
       </c>
-      <c r="AV8" s="62" t="s">
+      <c r="AV8" s="64" t="s">
         <v>144</v>
       </c>
-      <c r="AW8" s="62" t="s">
+      <c r="AW8" s="64" t="s">
         <v>145</v>
       </c>
-      <c r="AX8" s="62" t="s">
+      <c r="AX8" s="64" t="s">
         <v>146</v>
       </c>
       <c r="AY8" s="54"/>
       <c r="AZ8" s="54"/>
-      <c r="BA8" s="62"/>
-      <c r="BB8" s="62"/>
-      <c r="BC8" s="62"/>
-      <c r="BD8" s="62"/>
-      <c r="BE8" s="62"/>
-      <c r="BF8" s="62"/>
-      <c r="BG8" s="62"/>
-      <c r="BH8" s="63" t="n">
+      <c r="BA8" s="64"/>
+      <c r="BB8" s="64"/>
+      <c r="BC8" s="64"/>
+      <c r="BD8" s="64"/>
+      <c r="BE8" s="64"/>
+      <c r="BF8" s="64"/>
+      <c r="BG8" s="64"/>
+      <c r="BH8" s="65" t="n">
         <v>0.00078</v>
       </c>
       <c r="BI8" s="51" t="s">
         <v>147</v>
       </c>
       <c r="BJ8" s="51"/>
-      <c r="BK8" s="64" t="n">
+      <c r="BK8" s="66" t="n">
         <v>0.00084</v>
       </c>
       <c r="BL8" s="52"/>
